--- a/sitepreview/trust/ValueSet-Participants-UAT.xlsx
+++ b/sitepreview/trust/ValueSet-Participants-UAT.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="82">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.0</t>
+    <t>1.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-27T08:38:34+00:00</t>
+    <t>2026-02-03T22:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>http://smart.who.int/refmart/CodeSystems/REF_COUNTRY</t>
+  </si>
+  <si>
+    <t>IOM</t>
   </si>
   <si>
     <t>XXA</t>
@@ -815,7 +818,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -832,13 +835,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2"/>
     </row>
@@ -898,17 +901,23 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>30</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B14" t="s" s="2">
+      <c r="B15" t="s" s="2">
         <v>32</v>
       </c>
     </row>

--- a/sitepreview/trust/ValueSet-Participants-UAT.xlsx
+++ b/sitepreview/trust/ValueSet-Participants-UAT.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T22:38:59+00:00</t>
+    <t>2026-02-04T13:15:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/ValueSet-Participants-UAT.xlsx
+++ b/sitepreview/trust/ValueSet-Participants-UAT.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:15:56+00:00</t>
+    <t>2026-02-04T15:17:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/ValueSet-Participants-UAT.xlsx
+++ b/sitepreview/trust/ValueSet-Participants-UAT.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T15:17:54+00:00</t>
+    <t>2026-02-04T18:55:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/ValueSet-Participants-UAT.xlsx
+++ b/sitepreview/trust/ValueSet-Participants-UAT.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4.0</t>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T14:17:30+00:00</t>
+    <t>2026-04-27T07:32:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sitepreview/trust/ValueSet-Participants-UAT.xlsx
+++ b/sitepreview/trust/ValueSet-Participants-UAT.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="86">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T07:32:49+00:00</t>
+    <t>2026-07-01T12:00:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -146,6 +146,9 @@
     <t>CZE</t>
   </si>
   <si>
+    <t>ECU</t>
+  </si>
+  <si>
     <t>ESP</t>
   </si>
   <si>
@@ -161,6 +164,9 @@
     <t>FRO</t>
   </si>
   <si>
+    <t>GTM</t>
+  </si>
+  <si>
     <t>HRV</t>
   </si>
   <si>
@@ -206,6 +212,9 @@
     <t>SGP</t>
   </si>
   <si>
+    <t>SLV</t>
+  </si>
+  <si>
     <t>SMR</t>
   </si>
   <si>
@@ -246,6 +255,9 @@
   </si>
   <si>
     <t>XXO</t>
+  </si>
+  <si>
+    <t>XXQ</t>
   </si>
   <si>
     <t>XXS</t>
@@ -564,7 +576,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -797,18 +809,36 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>30</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="B38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B40" s="2"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B39" t="s" s="2">
-        <v>70</v>
+      <c r="B42" t="s" s="2">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -818,7 +848,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -835,7 +865,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2"/>
     </row>
@@ -847,77 +877,83 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>30</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B15" t="s" s="2">
+      <c r="B16" t="s" s="2">
         <v>32</v>
       </c>
     </row>
